--- a/ci-cd-merge-resolver/repoCollector/datasets/hive.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/hive.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,24 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>651e7950977dd4e63da42648c38b03c3bf097e7f</t>
+  </si>
+  <si>
+    <t>f0a2fffa9e7044002c6b75219fd3da50b55c3e68</t>
+  </si>
+  <si>
+    <t>851c8aba86aa027cc5aa21e8b71e04a1243c35b9</t>
+  </si>
+  <si>
+    <t>d2c60f3ae18fb18b1bc50355a7740cf352cab782</t>
+  </si>
+  <si>
+    <t>e8d7cdcc372e14f8a0a664911b5ae6934201e30b</t>
+  </si>
+  <si>
+    <t>90d19acd2b4f8301847ef13b4c8a91df3eafc65d</t>
+  </si>
+  <si>
     <t>4cc7819d77dc32ac44f857b8ed742439da68c56f</t>
   </si>
   <si>
@@ -53,6 +71,42 @@
     <t>6a8f4cbe328608a29f04c97c47b9d8c17f4ae29e</t>
   </si>
   <si>
+    <t>93b9cdd6945c30a46dab77cdee894a15c3fd8ca5</t>
+  </si>
+  <si>
+    <t>b95dc96ecbce8596efbe168e74c18f344538c5a2</t>
+  </si>
+  <si>
+    <t>20eb7b516f373f42b07f979ba03363c116adb99c</t>
+  </si>
+  <si>
+    <t>37a1907be4ecff19777a86f8b3d860861613af15</t>
+  </si>
+  <si>
+    <t>1c9947f38ba44a3c37469490669b37dae2b19b4c</t>
+  </si>
+  <si>
+    <t>bac1d98c5e91cdb39567f21b2068e7951a93ef44</t>
+  </si>
+  <si>
+    <t>cd8f693c078d78198e5f7c750d3cfd55aa218383</t>
+  </si>
+  <si>
+    <t>222b4aca081529d534f94cece1f9af79a0fb3dda</t>
+  </si>
+  <si>
+    <t>1b3ac733f53598636870f4f7af09d2938fe0b09f</t>
+  </si>
+  <si>
+    <t>4db8b1c66c459d6c0487565c3c176055a910da2a</t>
+  </si>
+  <si>
+    <t>d7bbc20d2e9b1cb460a9325698692b74802bae78</t>
+  </si>
+  <si>
+    <t>2ca70b91917b8ce668a6fd277a32ab4f2c9a68c0</t>
+  </si>
+  <si>
     <t>4743c7984d8a547cab135f9fc0fc550ac32dd61f</t>
   </si>
   <si>
@@ -62,58 +116,151 @@
     <t>6d532e7c4396a81b0afd16b66b4873c5fe9398ee</t>
   </si>
   <si>
-    <t>cd8f693c078d78198e5f7c750d3cfd55aa218383</t>
-  </si>
-  <si>
-    <t>222b4aca081529d534f94cece1f9af79a0fb3dda</t>
-  </si>
-  <si>
-    <t>1b3ac733f53598636870f4f7af09d2938fe0b09f</t>
-  </si>
-  <si>
-    <t>4db8b1c66c459d6c0487565c3c176055a910da2a</t>
-  </si>
-  <si>
-    <t>d7bbc20d2e9b1cb460a9325698692b74802bae78</t>
-  </si>
-  <si>
-    <t>2ca70b91917b8ce668a6fd277a32ab4f2c9a68c0</t>
-  </si>
-  <si>
-    <t>93b9cdd6945c30a46dab77cdee894a15c3fd8ca5</t>
-  </si>
-  <si>
-    <t>b95dc96ecbce8596efbe168e74c18f344538c5a2</t>
-  </si>
-  <si>
-    <t>20eb7b516f373f42b07f979ba03363c116adb99c</t>
-  </si>
-  <si>
-    <t>d2c60f3ae18fb18b1bc50355a7740cf352cab782</t>
-  </si>
-  <si>
-    <t>e8d7cdcc372e14f8a0a664911b5ae6934201e30b</t>
-  </si>
-  <si>
-    <t>90d19acd2b4f8301847ef13b4c8a91df3eafc65d</t>
-  </si>
-  <si>
-    <t>651e7950977dd4e63da42648c38b03c3bf097e7f</t>
-  </si>
-  <si>
-    <t>f0a2fffa9e7044002c6b75219fd3da50b55c3e68</t>
-  </si>
-  <si>
-    <t>851c8aba86aa027cc5aa21e8b71e04a1243c35b9</t>
-  </si>
-  <si>
-    <t>37a1907be4ecff19777a86f8b3d860861613af15</t>
-  </si>
-  <si>
-    <t>1c9947f38ba44a3c37469490669b37dae2b19b4c</t>
-  </si>
-  <si>
-    <t>bac1d98c5e91cdb39567f21b2068e7951a93ef44</t>
+    <t>14c9482017f5bb7263e0893023cc47a8d37ec3de</t>
+  </si>
+  <si>
+    <t>640159726f4406e752e9555b0b9a54452d8e9157</t>
+  </si>
+  <si>
+    <t>d376157bb507f251e121b59e7c2de9d96061d1b0</t>
+  </si>
+  <si>
+    <t>1fb04f36619483cc5a64e5963ddb8a097a68c9ba</t>
+  </si>
+  <si>
+    <t>7a40541f5f2d302e4577c5c57b4b0b7e1ae13fa8</t>
+  </si>
+  <si>
+    <t>56083008b596f410e030551e8884761b151d8bdd</t>
+  </si>
+  <si>
+    <t>379d9babdd43d459b0acfb7663527850320fdbb6</t>
+  </si>
+  <si>
+    <t>5b3c79798e28fd3c7f5718e361efee0f77eec047</t>
+  </si>
+  <si>
+    <t>fb07a1157b0b99cf51a3965e79b2c46e1845f5ee</t>
+  </si>
+  <si>
+    <t>42335b46cacb2ebcc4569e1081a1cc6369558146</t>
+  </si>
+  <si>
+    <t>c25455746ae46af61e44591ba3ee4833f0b4b8d0</t>
+  </si>
+  <si>
+    <t>08edf03f6338b4b43b53e9310faa8d38460e4b4f</t>
+  </si>
+  <si>
+    <t>77511070dd8b7176e98454b9a7010eedfbd5d981</t>
+  </si>
+  <si>
+    <t>6e0c52e6883cb55de3b8557504c13f3c8dfb619f</t>
+  </si>
+  <si>
+    <t>144efb0fcc8b74484c860e3559666a313641c93d</t>
+  </si>
+  <si>
+    <t>52e0f8f34076fda56888b773f9e603323d7a0fc5</t>
+  </si>
+  <si>
+    <t>4cd425132e54d7c48aa87fb8509b6011f5139862</t>
+  </si>
+  <si>
+    <t>21c209e324649a56e7928ccfcb2211bbff8e089e</t>
+  </si>
+  <si>
+    <t>2fa4dc277e0cd28261602c392c2f55d040d22677</t>
+  </si>
+  <si>
+    <t>ccea0d6ff7aaeaac494d7c7c680a3efad7805e3d</t>
+  </si>
+  <si>
+    <t>8e6719df622d03ba337f29cecaa2eac6095eb433</t>
+  </si>
+  <si>
+    <t>2a8d1bf658d3a2ff21f51e2607f7f78716a87b53</t>
+  </si>
+  <si>
+    <t>78f28c8855f9a2867c81f911cf56684c09a35ea9</t>
+  </si>
+  <si>
+    <t>d9e4ae09e66f97cee155b3c1b3ae7bc0cac02641</t>
+  </si>
+  <si>
+    <t>ee3a3ed35b337ff13156c6c6e27dd332cdee2009</t>
+  </si>
+  <si>
+    <t>ea95b712618bc922c028e2e67c45739fd38fd28a</t>
+  </si>
+  <si>
+    <t>5242f71cb2dfa24368fc8a7b5e9425d28b813f7b</t>
+  </si>
+  <si>
+    <t>be47d9e3fae437c7644e47679119d20b86f8a332</t>
+  </si>
+  <si>
+    <t>2014ece97960f8d2f690f55c131d9a61c421c2f9</t>
+  </si>
+  <si>
+    <t>1f0a5ef31c450db497052300a44a1080add47c6a</t>
+  </si>
+  <si>
+    <t>b8d7192f5f28dbc832d4de3e4afc763523a4bf12</t>
+  </si>
+  <si>
+    <t>f1f21e9975e088cb6064130f63712ceff8e1b864</t>
+  </si>
+  <si>
+    <t>45b48d5fdc3527e56347b297d1a41902d1313220</t>
+  </si>
+  <si>
+    <t>1ceaf357bbc27a42e10344e01f7da69a0df4b913</t>
+  </si>
+  <si>
+    <t>ed64a74e864e17c615fc8dede2a5272d3a18bcb3</t>
+  </si>
+  <si>
+    <t>e4856ca031ce4776ea8738824e57b213394a7735</t>
+  </si>
+  <si>
+    <t>18d133857b7930242538b49f33b3ca517b2e287d</t>
+  </si>
+  <si>
+    <t>42a38577bc9d242bed040c503b0d1d46f74e0301</t>
+  </si>
+  <si>
+    <t>8482c5fbe9d2b9a62132e0e94d5578a5eaa22fbd</t>
+  </si>
+  <si>
+    <t>81853c12e3ad2ec3f00c4631bbfeadf1c89ae4e4</t>
+  </si>
+  <si>
+    <t>b82d38aa38f71a66bee47977c041e7d8a28c8419</t>
+  </si>
+  <si>
+    <t>9a9f25409f4db9b3798aa529bb5531264cecd282</t>
+  </si>
+  <si>
+    <t>bb1c0f25fc17d8c5ced8855a05b6651358c5fd96</t>
+  </si>
+  <si>
+    <t>50fb6f3cb4651be5a1e0c0bae1f59f193f2c7e09</t>
+  </si>
+  <si>
+    <t>b7670c479893a17fcac41b06428c125de57b6c66</t>
+  </si>
+  <si>
+    <t>748c1bd2fa2942459e88e26e9820ebe3b3dd1fb5</t>
+  </si>
+  <si>
+    <t>3e01ef3268ffbcb69c5c18c2c9f8810512c91bf8</t>
+  </si>
+  <si>
+    <t>d00196c19fd4fd12db757b99ebb186d344fd3ba3</t>
+  </si>
+  <si>
+    <t>a67eb03c80000c89e5f19d5d1e62c35a63b32f3a</t>
   </si>
 </sst>
 </file>
@@ -158,7 +305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -207,10 +354,10 @@
         <v>188.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -219,10 +366,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>62.189002990722656</v>
+        <v>62.355003356933594</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -239,7 +386,7 @@
         <v>188.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="F3" t="n" s="0">
         <v>2.0</v>
@@ -251,10 +398,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>65.41899108886719</v>
+        <v>58.520999908447266</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -271,7 +418,7 @@
         <v>188.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>1.0</v>
@@ -283,10 +430,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>70.3810043334961</v>
+        <v>63.589996337890625</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -303,10 +450,10 @@
         <v>188.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>12.0</v>
+        <v>65.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>6.0</v>
+        <v>40.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -315,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>70.09100341796875</v>
+        <v>59.89900207519531</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -335,10 +482,10 @@
         <v>188.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>65.0</v>
+        <v>19.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>40.0</v>
+        <v>10.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -347,10 +494,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>61.40999984741211</v>
+        <v>62.811004638671875</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -367,10 +514,10 @@
         <v>188.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -379,10 +526,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>63.70499801635742</v>
+        <v>59.78499984741211</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -399,10 +546,10 @@
         <v>188.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>44.0</v>
+        <v>12.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>32.0</v>
+        <v>6.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -411,10 +558,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>61.10600280761719</v>
+        <v>63.698001861572266</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -431,10 +578,10 @@
         <v>188.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>19.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -443,10 +590,586 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>70.03099822998047</v>
+        <v>58.76399612426758</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>56.47600173950195</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>56.85000228881836</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>55.22200012207031</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>181.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>53.01499938964844</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>54.479000091552734</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>57.279998779296875</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D16" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G16" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>61.91599655151367</v>
+      </c>
+      <c r="J16" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="D17" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="E17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F17" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G17" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>54.13600158691406</v>
+      </c>
+      <c r="J17" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D18" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F18" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G18" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>60.12399673461914</v>
+      </c>
+      <c r="J18" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D19" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="E19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G19" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>57.6609992980957</v>
+      </c>
+      <c r="J19" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D20" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="E20" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G20" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>57.28600311279297</v>
+      </c>
+      <c r="J20" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D21" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="E21" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F21" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G21" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>56.3910026550293</v>
+      </c>
+      <c r="J21" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D22" t="n" s="0">
+        <v>140.0</v>
+      </c>
+      <c r="E22" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="F22" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="G22" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>60.98699951171875</v>
+      </c>
+      <c r="J22" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D23" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E23" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F23" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G23" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>66.8189926147461</v>
+      </c>
+      <c r="J23" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D24" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E24" t="n" s="0">
+        <v>34.0</v>
+      </c>
+      <c r="F24" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="G24" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>65.64500427246094</v>
+      </c>
+      <c r="J24" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D25" t="n" s="0">
+        <v>165.0</v>
+      </c>
+      <c r="E25" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F25" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G25" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H25" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>71.32901000976562</v>
+      </c>
+      <c r="J25" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="D26" t="n" s="0">
+        <v>133.0</v>
+      </c>
+      <c r="E26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G26" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>68.53400421142578</v>
+      </c>
+      <c r="J26" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D27" t="n" s="0">
+        <v>131.0</v>
+      </c>
+      <c r="E27" t="n" s="0">
+        <v>36.0</v>
+      </c>
+      <c r="F27" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="G27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>56.03700256347656</v>
+      </c>
+      <c r="J27" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
